--- a/data/trans_dic/P2C_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,54</t>
+          <t>0,0; 48,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,57</t>
+          <t>0,0; 23,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 25,78</t>
+          <t>2,74; 26,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,29; 2,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,57</t>
+          <t>0,0; 26,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,66</t>
+          <t>0,23; 1,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,1</t>
+          <t>0,26; 2,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,45</t>
+          <t>0,33; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,21</t>
+          <t>0,49; 2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,43</t>
+          <t>0,23; 2,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,1</t>
+          <t>0,81; 3,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,57</t>
+          <t>0,49; 2,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,25</t>
+          <t>0,72; 3,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,24</t>
+          <t>0,61; 2,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,37</t>
+          <t>0,72; 2,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,26</t>
+          <t>0,71; 2,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,04</t>
+          <t>0,39; 3,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,27</t>
+          <t>0,26; 2,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,34</t>
+          <t>0,91; 4,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,07</t>
+          <t>4,84; 17,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,48</t>
+          <t>0,36; 3,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,07</t>
+          <t>0,34; 3,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,58</t>
+          <t>4,23; 12,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,15</t>
+          <t>0,17; 1,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,2</t>
+          <t>0,46; 2,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,05</t>
+          <t>0,96; 3,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,21</t>
+          <t>5,38; 12,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,84; 29,25</t>
+          <t>10,81; 28,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,55</t>
+          <t>0,94; 6,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,92</t>
+          <t>5,3; 17,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,9</t>
+          <t>0,82; 3,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,52</t>
+          <t>0,29; 2,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 19,94</t>
+          <t>9,29; 20,09</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,32; 33,11</t>
+          <t>14,08; 33,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,75</t>
+          <t>0,31; 3,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 26,22</t>
+          <t>1,32; 26,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,31</t>
+          <t>0,16; 1,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,25</t>
+          <t>0,15; 1,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,77</t>
+          <t>0,3; 1,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 25,16</t>
+          <t>1,91; 25,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,96; 55,35</t>
+          <t>39,03; 55,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,12</t>
+          <t>0,55; 3,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,66</t>
+          <t>0,32; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,1; 52,01</t>
+          <t>41,52; 51,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,37</t>
+          <t>0,35; 2,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>0,32; 2,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,62; 51,51</t>
+          <t>42,29; 51,43</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,08</t>
+          <t>0,29; 1,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,25</t>
+          <t>0,46; 1,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,43</t>
+          <t>0,57; 1,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,68; 20,03</t>
+          <t>13,65; 20,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,29</t>
+          <t>0,44; 1,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,66</t>
+          <t>0,72; 1,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,54</t>
+          <t>0,64; 1,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,09</t>
+          <t>7,22; 18,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,06</t>
+          <t>0,44; 0,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,32</t>
+          <t>0,68; 1,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,29</t>
+          <t>0,66; 1,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,71</t>
+          <t>8,58; 17,73</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1887</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1946</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 12693</t>
+          <t>0; 12519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1812</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1886</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7587</t>
+          <t>0; 7579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1855</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1524; 14907</t>
+          <t>1582; 15512</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10015</t>
+          <t>0; 9852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7685</t>
+          <t>936; 7648</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5801</t>
+          <t>0; 5326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 17144</t>
+          <t>0; 13825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7845</t>
+          <t>0; 7780</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 12545</t>
+          <t>0; 11504</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1870</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 888</t>
+          <t>0; 851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1210; 11892</t>
+          <t>1646; 12784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1937; 15666</t>
+          <t>1919; 16057</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6085</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 17376</t>
+          <t>0; 13645</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>872; 12493</t>
+          <t>1701; 12910</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2891; 18278</t>
+          <t>2804; 16586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1608; 11269</t>
+          <t>1062; 11508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7007</t>
+          <t>0; 7281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4282; 18284</t>
+          <t>4751; 17940</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2998; 15687</t>
+          <t>3018; 15785</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4486; 17594</t>
+          <t>3920; 16883</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5147</t>
+          <t>0; 5286</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7603; 24599</t>
+          <t>6684; 23194</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8721; 27902</t>
+          <t>8460; 26734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7520; 22758</t>
+          <t>7096; 23600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1154; 10193</t>
+          <t>977; 9441</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4983</t>
+          <t>0; 4748</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>959; 8528</t>
+          <t>967; 8429</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3225; 14759</t>
+          <t>3097; 14125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5208; 18714</t>
+          <t>5014; 18377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 9199</t>
+          <t>0; 10926</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1102; 10703</t>
+          <t>1096; 10801</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1072; 9688</t>
+          <t>1086; 9756</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4820; 13995</t>
+          <t>4711; 13921</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>903; 11356</t>
+          <t>899; 10313</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3206; 15006</t>
+          <t>3151; 14987</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6365; 20025</t>
+          <t>6276; 20177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11767; 28375</t>
+          <t>11567; 27542</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7508</t>
+          <t>0; 6704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6920; 18668</t>
+          <t>6901; 18326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6999</t>
+          <t>0; 6175</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2974; 14552</t>
+          <t>2080; 13798</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4850</t>
+          <t>0; 5051</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3944; 11747</t>
+          <t>3681; 11897</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6130</t>
+          <t>0; 6123</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2908; 14193</t>
+          <t>2980; 14288</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>967; 8434</t>
+          <t>958; 9092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12611; 26576</t>
+          <t>12379; 26764</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6788</t>
+          <t>0; 8278</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7222</t>
+          <t>0; 7164</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5276</t>
+          <t>0; 4826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5646; 14038</t>
+          <t>5967; 14129</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5248</t>
+          <t>0; 5399</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4897</t>
+          <t>0; 5624</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1027; 9506</t>
+          <t>1083; 10381</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3686; 70633</t>
+          <t>3544; 71579</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1041; 8329</t>
+          <t>1035; 8451</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>974; 8223</t>
+          <t>976; 8234</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2058; 11480</t>
+          <t>1969; 11367</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5684; 78435</t>
+          <t>5965; 79921</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>0; 4493</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5035</t>
+          <t>0; 5746</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5631</t>
+          <t>0; 6251</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32707; 46471</t>
+          <t>32766; 46789</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5133</t>
+          <t>0; 6482</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2150; 12031</t>
+          <t>2121; 12041</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1247; 10458</t>
+          <t>1256; 11500</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>75586; 95661</t>
+          <t>76361; 95339</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6418</t>
+          <t>0; 6851</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2276; 15012</t>
+          <t>2221; 13329</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2052; 13202</t>
+          <t>2054; 12850</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>114165; 137978</t>
+          <t>113274; 137770</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4736; 20677</t>
+          <t>5479; 20075</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9457; 26765</t>
+          <t>9727; 28419</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10603; 27109</t>
+          <t>10835; 27175</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66947; 97983</t>
+          <t>66767; 99445</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10664; 29730</t>
+          <t>10194; 28173</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18997; 41757</t>
+          <t>18056; 41584</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14413; 35890</t>
+          <t>14921; 33490</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>57911; 162248</t>
+          <t>64709; 162854</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19490; 44763</t>
+          <t>18664; 41428</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32174; 61541</t>
+          <t>31692; 61375</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29413; 54728</t>
+          <t>28035; 54523</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>120183; 245408</t>
+          <t>118878; 245815</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,86</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 14,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 26,83</t>
+          <t>1,85; 19,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,39</t>
+          <t>0,29; 2,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,27</t>
+          <t>0,0; 30,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,79</t>
+          <t>0,14; 1,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,15</t>
+          <t>0,26; 2,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,2</t>
+          <t>0,0; 10,04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,53</t>
+          <t>0,17; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,91</t>
+          <t>0,49; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,48</t>
+          <t>0,23; 2,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,04</t>
+          <t>0,75; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,59</t>
+          <t>0,61; 2,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,12</t>
+          <t>0,83; 3,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,11</t>
+          <t>0,66; 2,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,27</t>
+          <t>0,71; 2,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,35</t>
+          <t>0,73; 2,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,74</t>
+          <t>0,36; 3,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,25</t>
+          <t>0,26; 2,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,15</t>
+          <t>0,93; 4,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,74</t>
+          <t>4,27; 15,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,51</t>
+          <t>0,35; 3,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,09</t>
+          <t>0,34; 3,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,51</t>
+          <t>4,39; 11,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,95</t>
+          <t>0,17; 1,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,19</t>
+          <t>0,46; 2,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,08</t>
+          <t>0,94; 3,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 12,82</t>
+          <t>5,46; 12,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 28,72</t>
+          <t>9,97; 28,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,21</t>
+          <t>1,36; 5,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,13</t>
+          <t>5,24; 16,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,93</t>
+          <t>0,7; 3,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,72</t>
+          <t>0,29; 2,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 20,09</t>
+          <t>8,95; 19,48</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -1417,42 +1417,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 33,33</t>
+          <t>13,8; 33,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,0</t>
+          <t>0,31; 3,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 26,57</t>
+          <t>16,97; 32,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,26</t>
+          <t>0,15; 1,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,76</t>
+          <t>0,3; 1,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 25,63</t>
+          <t>17,49; 29,38</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,03; 55,73</t>
+          <t>37,76; 54,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,12</t>
+          <t>0,54; 2,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,92</t>
+          <t>0,32; 3,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,52; 51,84</t>
+          <t>40,5; 51,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,1</t>
+          <t>0,48; 2,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,01</t>
+          <t>0,25; 1,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,29; 51,43</t>
+          <t>41,68; 50,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,05</t>
+          <t>0,32; 1,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,33</t>
+          <t>0,44; 1,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,43</t>
+          <t>0,55; 1,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,65; 20,33</t>
+          <t>12,54; 18,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,22</t>
+          <t>0,46; 1,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,65</t>
+          <t>0,78; 1,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,43</t>
+          <t>0,63; 1,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 18,16</t>
+          <t>14,65; 18,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,98</t>
+          <t>0,44; 0,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,32</t>
+          <t>0,7; 1,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,29</t>
+          <t>0,69; 1,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 17,73</t>
+          <t>14,42; 17,87</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5834</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 12519</t>
+          <t>0; 12558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7579</t>
+          <t>0; 6495</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1582; 15512</t>
+          <t>1406; 15148</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>5313</t>
         </is>
       </c>
     </row>
@@ -2276,32 +2276,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9852</t>
+          <t>0; 9076</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>936; 7648</t>
+          <t>920; 7692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5326</t>
+          <t>0; 5113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 13825</t>
+          <t>0; 20665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7780</t>
+          <t>0; 7610</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 11504</t>
+          <t>0; 14062</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2311,27 +2311,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 851</t>
+          <t>0; 7623</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1646; 12784</t>
+          <t>1030; 11644</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1919; 16057</t>
+          <t>1905; 15261</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>0; 5097</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 13645</t>
+          <t>0; 17933</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3530</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1701; 12910</t>
+          <t>875; 12481</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2804; 16586</t>
+          <t>2787; 16507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1062; 11508</t>
+          <t>1070; 12138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7281</t>
+          <t>0; 6980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4751; 17940</t>
+          <t>4394; 18030</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3018; 15785</t>
+          <t>3718; 16633</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3920; 16883</t>
+          <t>4468; 17596</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5286</t>
+          <t>0; 5436</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6684; 23194</t>
+          <t>7220; 23660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8460; 26734</t>
+          <t>8341; 26826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7096; 23600</t>
+          <t>7372; 24742</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>977; 9441</t>
+          <t>1050; 8856</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>20412</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4748</t>
+          <t>0; 4495</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>967; 8429</t>
+          <t>959; 8543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3097; 14125</t>
+          <t>3174; 14815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5014; 18377</t>
+          <t>5052; 18435</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 10926</t>
+          <t>0; 10336</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1096; 10801</t>
+          <t>1075; 10726</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1086; 9756</t>
+          <t>1076; 9640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4711; 13921</t>
+          <t>5596; 14988</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>899; 10313</t>
+          <t>899; 10053</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3151; 14987</t>
+          <t>3148; 14025</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6276; 20177</t>
+          <t>6140; 20061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11567; 27542</t>
+          <t>13405; 29589</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19506</t>
         </is>
       </c>
     </row>
@@ -2910,52 +2910,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6704</t>
+          <t>0; 6676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6901; 18326</t>
+          <t>6872; 19452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6175</t>
+          <t>0; 5478</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2080; 13798</t>
+          <t>3015; 13233</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5051</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3681; 11897</t>
+          <t>4089; 12508</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6123</t>
+          <t>0; 6204</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2980; 14288</t>
+          <t>2543; 13905</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>958; 9092</t>
+          <t>966; 8578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12379; 26764</t>
+          <t>13144; 28619</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>27809</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8278</t>
+          <t>0; 7242</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7164</t>
+          <t>0; 6400</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4826</t>
+          <t>0; 5491</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5967; 14129</t>
+          <t>6386; 15286</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5399</t>
+          <t>0; 7055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5624</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1083; 10381</t>
+          <t>1076; 10415</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3544; 71579</t>
+          <t>12317; 23308</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1035; 8451</t>
+          <t>1041; 8450</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>976; 8234</t>
+          <t>969; 8883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1969; 11367</t>
+          <t>1967; 11460</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5965; 79921</t>
+          <t>20787; 34910</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>41562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>86062</t>
+          <t>92429</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>126028</t>
+          <t>133990</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4232</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5746</t>
+          <t>0; 5999</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6251</t>
+          <t>0; 5542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32766; 46789</t>
+          <t>34147; 49093</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6482</t>
+          <t>0; 5692</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2121; 12041</t>
+          <t>2090; 11252</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1256; 11500</t>
+          <t>1264; 11819</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>76361; 95339</t>
+          <t>80789; 101831</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6851</t>
+          <t>0; 6273</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2221; 13329</t>
+          <t>3056; 13136</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2054; 12850</t>
+          <t>1594; 12520</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>113274; 137770</t>
+          <t>120837; 146696</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>216395</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5479; 20075</t>
+          <t>6058; 20774</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9727; 28419</t>
+          <t>9478; 27855</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10835; 27175</t>
+          <t>10481; 28089</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66767; 99445</t>
+          <t>70340; 105299</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10194; 28173</t>
+          <t>10648; 29809</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18056; 41584</t>
+          <t>19644; 43059</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14921; 33490</t>
+          <t>14748; 33957</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64709; 162854</t>
+          <t>115664; 147593</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18664; 41428</t>
+          <t>18714; 41885</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31692; 61375</t>
+          <t>32674; 62658</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28035; 54523</t>
+          <t>29164; 56166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>118878; 245815</t>
+          <t>194694; 241368</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
